--- a/reports/pdf_change_20260701.xlsx
+++ b/reports/pdf_change_20260701.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -166,6 +166,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -535,16 +541,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -573,6 +581,8 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -582,13 +592,15 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="n"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -598,25 +610,35 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -631,20 +653,26 @@
       <c r="B6" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="n">
+        <v>2363517200</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>111→133</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="G6" s="14" t="n">
         <v>-19</v>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="H6" s="14" t="n">
+        <v>-1628653400</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>76→57</t>
         </is>
@@ -659,20 +687,26 @@
       <c r="B7" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="n">
+        <v>2607231000</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>25→40</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="G7" s="14" t="n">
         <v>-19</v>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="H7" s="14" t="n">
+        <v>-1719025000</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>38→19</t>
         </is>
@@ -682,15 +716,19 @@
       <c r="A8" s="15" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="15" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="D8" s="15" t="n"/>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>두산테스나</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="G8" s="14" t="n">
         <v>-13</v>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="H8" s="14" t="n">
+        <v>-1563304600</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>74→61</t>
         </is>
@@ -708,6 +746,8 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -728,6 +768,8 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -737,13 +779,15 @@
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="n"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -753,25 +797,35 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -786,20 +840,26 @@
       <c r="B16" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="n">
+        <v>2470305600</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>19→40</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="G16" s="14" t="n">
         <v>-39</v>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="H16" s="14" t="n">
+        <v>-3063387600</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>189→150</t>
         </is>
@@ -817,6 +877,8 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -837,6 +899,8 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -846,13 +910,15 @@
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="n"/>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -862,25 +928,35 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>변화(1CU주)</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>변화</t>
-        </is>
-      </c>
       <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -895,20 +971,30 @@
       <c r="B24" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>2,940→3,020</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="G24" s="14" t="n">
         <v>-40</v>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>796→756</t>
         </is>
@@ -923,20 +1009,30 @@
       <c r="B25" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>610→655</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>스피어</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="G25" s="14" t="n">
         <v>-35</v>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>647→612</t>
         </is>
@@ -951,20 +1047,30 @@
       <c r="B26" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>58→85</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="G26" s="14" t="n">
         <v>-9</v>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>116→107</t>
         </is>
@@ -982,6 +1088,8 @@
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -991,38 +1099,40 @@
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260701.xlsx
+++ b/reports/pdf_change_20260701.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+    <numFmt numFmtId="165" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;;0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -132,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -157,11 +158,17 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -541,18 +548,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -572,7 +581,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      당일 2026-07-01  vs  전영업일 2026-06-30      매수 2종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,782억      당일 2026-07-01  vs  전영업일 2026-06-30      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -583,6 +592,8 @@
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -593,14 +604,16 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -620,25 +633,35 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -656,23 +679,29 @@
       <c r="C6" s="11" t="n">
         <v>2363517200</v>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="12" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>111→133</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>-1628653400</v>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="J6" s="16" t="n">
+        <v>-0.282</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>76→57</t>
         </is>
@@ -690,45 +719,55 @@
       <c r="C7" s="11" t="n">
         <v>2607231000</v>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="12" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>25→40</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>파두</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>-1719025000</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="J7" s="16" t="n">
+        <v>-0.297</v>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>38→19</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>두산테스나</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="H8" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>-1563304600</v>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="J8" s="16" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>74→61</t>
         </is>
@@ -737,7 +776,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      당일 2026-07-01  vs  전영업일 2026-06-30      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,784억      당일 2026-07-01  vs  전영업일 2026-06-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -748,9 +787,11 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -759,7 +800,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      당일 2026-07-01  vs  전영업일 2026-06-30      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,651억      당일 2026-07-01  vs  전영업일 2026-06-30      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -770,6 +811,8 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -780,14 +823,16 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -807,25 +852,35 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -843,23 +898,29 @@
       <c r="C16" s="11" t="n">
         <v>2470305600</v>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="12" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>19→40</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="H16" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="I16" s="15" t="n">
         <v>-3063387600</v>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="J16" s="16" t="n">
+        <v>-0.839</v>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>189→150</t>
         </is>
@@ -868,7 +929,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      당일 2026-07-01  vs  전영업일 2026-06-30      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,801억      당일 2026-07-01  vs  전영업일 2026-06-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -879,9 +940,11 @@
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -890,7 +953,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      당일 2026-07-01  vs  전영업일 2026-06-30      매수 3종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 376억      당일 2026-07-01  vs  전영업일 2026-06-30      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -901,6 +964,8 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -911,14 +976,16 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -938,25 +1005,35 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
@@ -971,30 +1048,40 @@
       <c r="B24" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>2,940→3,020</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="G24" s="14" t="n">
+      <c r="H24" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>796→756</t>
         </is>
@@ -1009,30 +1096,40 @@
       <c r="B25" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>610→655</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>스피어</t>
         </is>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="H25" s="15" t="n">
         <v>-35</v>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
         <is>
           <t>647→612</t>
         </is>
@@ -1047,30 +1144,40 @@
       <c r="B26" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>58→85</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="G26" s="14" t="n">
+      <c r="H26" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>116→107</t>
         </is>
@@ -1079,7 +1186,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-01  vs  전영업일 2026-06-30      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 613억      당일 2026-07-01  vs  전영업일 2026-06-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1090,49 +1197,53 @@
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260701.xlsx
+++ b/reports/pdf_change_20260701.xlsx
@@ -133,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -173,12 +173,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1048,15 +1042,11 @@
       <c r="B24" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="11" t="n">
+        <v>67497600</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0.179</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1071,15 +1061,11 @@
       <c r="H24" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="15" t="n">
+        <v>-124030000</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>-0.329</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1096,15 +1082,11 @@
       <c r="B25" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="11" t="n">
+        <v>186637500</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>0.496</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1119,15 +1101,11 @@
       <c r="H25" s="15" t="n">
         <v>-35</v>
       </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="15" t="n">
+        <v>-64562750</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <v>-0.172</v>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
@@ -1144,15 +1122,11 @@
       <c r="B26" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="11" t="n">
+        <v>47565900</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>0.126</v>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
@@ -1167,15 +1141,11 @@
       <c r="H26" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="15" t="n">
+        <v>-113760000</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>-0.302</v>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
@@ -1208,21 +1178,21 @@
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="22" t="n"/>
-      <c r="F31" s="22" t="n"/>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
